--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J506"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18656,6 +18656,114 @@
         <v>323.93</v>
       </c>
       <c r="J506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="C507" t="n">
+        <v>314.34</v>
+      </c>
+      <c r="D507" t="n">
+        <v>312.12</v>
+      </c>
+      <c r="E507" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="F507" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="G507" t="n">
+        <v>328.66</v>
+      </c>
+      <c r="H507" t="n">
+        <v>330.62</v>
+      </c>
+      <c r="I507" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>326.77</v>
+      </c>
+      <c r="C508" t="n">
+        <v>314.59</v>
+      </c>
+      <c r="D508" t="n">
+        <v>312.72</v>
+      </c>
+      <c r="E508" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="F508" t="n">
+        <v>331.33</v>
+      </c>
+      <c r="G508" t="n">
+        <v>329</v>
+      </c>
+      <c r="H508" t="n">
+        <v>330.73</v>
+      </c>
+      <c r="I508" t="n">
+        <v>324.32</v>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>325.9</v>
+      </c>
+      <c r="C509" t="n">
+        <v>314.17</v>
+      </c>
+      <c r="D509" t="n">
+        <v>312.28</v>
+      </c>
+      <c r="E509" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="F509" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="G509" t="n">
+        <v>328.19</v>
+      </c>
+      <c r="H509" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="I509" t="n">
+        <v>322.81</v>
+      </c>
+      <c r="J509" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18672,7 +18780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B576"/>
+  <dimension ref="A1:B579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24435,6 +24543,36 @@
       </c>
       <c r="B576" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -24603,28 +24741,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07657230584368226</v>
+        <v>-0.07665613785907469</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01244542093987988</v>
+        <v>0.01264503663935435</v>
       </c>
       <c r="M2" t="n">
-        <v>4.164491079828629</v>
+        <v>4.142287592178161</v>
       </c>
       <c r="N2" t="n">
-        <v>26.27642985408704</v>
+        <v>26.12261431578272</v>
       </c>
       <c r="O2" t="n">
-        <v>5.126054023719126</v>
+        <v>5.111028694478511</v>
       </c>
       <c r="P2" t="n">
-        <v>328.7001447177509</v>
+        <v>328.701032248603</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24681,28 +24819,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.268500540760664</v>
+        <v>-0.2648751801413139</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.113211622785705</v>
+        <v>0.1117251768417796</v>
       </c>
       <c r="M3" t="n">
-        <v>4.617575517099274</v>
+        <v>4.612820477126806</v>
       </c>
       <c r="N3" t="n">
-        <v>31.89265658794335</v>
+        <v>31.75765159890015</v>
       </c>
       <c r="O3" t="n">
-        <v>5.647358372544047</v>
+        <v>5.635392763499289</v>
       </c>
       <c r="P3" t="n">
-        <v>318.5894844638308</v>
+        <v>318.5512911982857</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24759,28 +24897,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2932631236485141</v>
+        <v>-0.2880739325769441</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1733787390422701</v>
+        <v>0.1696266024146913</v>
       </c>
       <c r="M4" t="n">
-        <v>3.89566315863825</v>
+        <v>3.904362741580369</v>
       </c>
       <c r="N4" t="n">
-        <v>23.01033161149813</v>
+        <v>22.98244891258042</v>
       </c>
       <c r="O4" t="n">
-        <v>4.796908547335266</v>
+        <v>4.794001346743701</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9825855383495</v>
+        <v>315.9276625097419</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24841,28 +24979,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1141326197185575</v>
+        <v>-0.1099596410733181</v>
       </c>
       <c r="J5" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04698335635422468</v>
+        <v>0.04414558785544942</v>
       </c>
       <c r="M5" t="n">
-        <v>2.955483841195407</v>
+        <v>2.960771817562519</v>
       </c>
       <c r="N5" t="n">
-        <v>14.9227000331901</v>
+        <v>14.90529650035168</v>
       </c>
       <c r="O5" t="n">
-        <v>3.86299107340285</v>
+        <v>3.860737818131617</v>
       </c>
       <c r="P5" t="n">
-        <v>331.2344275977495</v>
+        <v>331.1904655739306</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24919,28 +25057,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06665564530812146</v>
+        <v>0.06638726698455273</v>
       </c>
       <c r="J6" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K6" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01840096964882898</v>
+        <v>0.01850633355068898</v>
       </c>
       <c r="M6" t="n">
-        <v>2.575203865750274</v>
+        <v>2.562784408046471</v>
       </c>
       <c r="N6" t="n">
-        <v>13.3856256988227</v>
+        <v>13.30779934107285</v>
       </c>
       <c r="O6" t="n">
-        <v>3.658637136806915</v>
+        <v>3.647985655272353</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1887058023059</v>
+        <v>329.1915332570841</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24997,28 +25135,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2088281885250506</v>
+        <v>0.2080400574374809</v>
       </c>
       <c r="J7" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K7" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1172871051163457</v>
+        <v>0.1179350543183094</v>
       </c>
       <c r="M7" t="n">
-        <v>3.278636114802291</v>
+        <v>3.263480687454273</v>
       </c>
       <c r="N7" t="n">
-        <v>18.53612018222153</v>
+        <v>18.42982151581995</v>
       </c>
       <c r="O7" t="n">
-        <v>4.305359471893321</v>
+        <v>4.292996798952911</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6363455317484</v>
+        <v>323.6446504477158</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25075,28 +25213,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3582690002745434</v>
+        <v>0.3589211812820621</v>
       </c>
       <c r="J8" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K8" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2644595672939691</v>
+        <v>0.2678721003441894</v>
       </c>
       <c r="M8" t="n">
-        <v>3.465543550886944</v>
+        <v>3.448612830055589</v>
       </c>
       <c r="N8" t="n">
-        <v>20.16216302661944</v>
+        <v>20.04597565955448</v>
       </c>
       <c r="O8" t="n">
-        <v>4.490229729826686</v>
+        <v>4.477273239322622</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1461005568387</v>
+        <v>320.1392331376741</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25153,28 +25291,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3688985549638596</v>
+        <v>0.368371841929328</v>
       </c>
       <c r="J9" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K9" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2136195684105964</v>
+        <v>0.2154688736997383</v>
       </c>
       <c r="M9" t="n">
-        <v>3.818338669927999</v>
+        <v>3.798922675667043</v>
       </c>
       <c r="N9" t="n">
-        <v>28.29286732862473</v>
+        <v>28.12989015892652</v>
       </c>
       <c r="O9" t="n">
-        <v>5.319103996785993</v>
+        <v>5.303761887465021</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2858804112016</v>
+        <v>314.291435289916</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25212,7 +25350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J506"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51523,6 +51661,162 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-46.38324225114931,168.00940078209914</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-46.383137965955505,168.00852888113778</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-46.38305577045794,168.00778576165402</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-46.38284332803769,168.0069792831384</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-46.38251244318941,168.006215213545</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-46.38219203354017,168.0054454454251</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-46.38189922597754,168.00463943915972</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-46.38167228943793,168.00379329854346</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-46.383240095924286,168.00940086733826</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-46.3831402009472,168.00852856217875</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-46.38306065429301,168.00778246623454</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-46.382845056988245,168.00697742186068</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-46.38251870088338,168.0062093552231</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-46.382194620718124,168.0054430995484</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-46.381900118582365,168.00463882653662</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-46.38167245963232,168.00379321535263</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-46.38323228323361,168.00940117633</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-46.38313644616114,168.00852909802992</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-46.38305707281397,168.00778488287557</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-46.382841166849424,168.0069816097354</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-46.382512141613795,168.00621549587373</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-46.38218845714703,168.0054486882543</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-46.38189216628466,168.00464428445085</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-46.3816596099554,168.00379949625818</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18766,6 +18766,78 @@
       <c r="J509" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>325.26</v>
+      </c>
+      <c r="C510" t="n">
+        <v>312.93</v>
+      </c>
+      <c r="D510" t="n">
+        <v>310.69</v>
+      </c>
+      <c r="E510" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="F510" t="n">
+        <v>329.47</v>
+      </c>
+      <c r="G510" t="n">
+        <v>327.23</v>
+      </c>
+      <c r="H510" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="I510" t="n">
+        <v>321.88</v>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>326.27</v>
+      </c>
+      <c r="C511" t="n">
+        <v>313.35</v>
+      </c>
+      <c r="D511" t="n">
+        <v>310.88</v>
+      </c>
+      <c r="E511" t="n">
+        <v>330.47</v>
+      </c>
+      <c r="F511" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="G511" t="n">
+        <v>328.31</v>
+      </c>
+      <c r="H511" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="I511" t="n">
+        <v>323.1</v>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18780,7 +18852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B579"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24573,6 +24645,26 @@
       </c>
       <c r="B579" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -24741,28 +24833,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07665613785907469</v>
+        <v>-0.07733795493044909</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01264503663935435</v>
+        <v>0.01298361005478232</v>
       </c>
       <c r="M2" t="n">
-        <v>4.142287592178161</v>
+        <v>4.128888161270453</v>
       </c>
       <c r="N2" t="n">
-        <v>26.12261431578272</v>
+        <v>26.02405332629732</v>
       </c>
       <c r="O2" t="n">
-        <v>5.111028694478511</v>
+        <v>5.101377591033359</v>
       </c>
       <c r="P2" t="n">
-        <v>328.701032248603</v>
+        <v>328.70822881445</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24819,28 +24911,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2648751801413139</v>
+        <v>-0.2634863421944866</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1117251768417796</v>
+        <v>0.1115573174620068</v>
       </c>
       <c r="M3" t="n">
-        <v>4.612820477126806</v>
+        <v>4.603287709969972</v>
       </c>
       <c r="N3" t="n">
-        <v>31.75765159890015</v>
+        <v>31.64522887518218</v>
       </c>
       <c r="O3" t="n">
-        <v>5.635392763499289</v>
+        <v>5.625409218464216</v>
       </c>
       <c r="P3" t="n">
-        <v>318.5512911982857</v>
+        <v>318.5366274128198</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24897,28 +24989,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2880739325769441</v>
+        <v>-0.2859646913539473</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K4" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1696266024146913</v>
+        <v>0.16869095787019</v>
       </c>
       <c r="M4" t="n">
-        <v>3.904362741580369</v>
+        <v>3.901905190190914</v>
       </c>
       <c r="N4" t="n">
-        <v>22.98244891258042</v>
+        <v>22.91945801186486</v>
       </c>
       <c r="O4" t="n">
-        <v>4.794001346743701</v>
+        <v>4.787427076401777</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9276625097419</v>
+        <v>315.9052904939148</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24979,28 +25071,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1099596410733181</v>
+        <v>-0.1084794320353449</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04414558785544942</v>
+        <v>0.04335684068723167</v>
       </c>
       <c r="M5" t="n">
-        <v>2.960771817562519</v>
+        <v>2.957193094328434</v>
       </c>
       <c r="N5" t="n">
-        <v>14.90529650035168</v>
+        <v>14.86099263623957</v>
       </c>
       <c r="O5" t="n">
-        <v>3.860737818131617</v>
+        <v>3.854995802363418</v>
       </c>
       <c r="P5" t="n">
-        <v>331.1904655739306</v>
+        <v>331.1748364702594</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25057,28 +25149,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06638726698455273</v>
+        <v>0.06551489556220545</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01850633355068898</v>
+        <v>0.01818834146760917</v>
       </c>
       <c r="M6" t="n">
-        <v>2.562784408046471</v>
+        <v>2.557473330383518</v>
       </c>
       <c r="N6" t="n">
-        <v>13.30779934107285</v>
+        <v>13.26098744162149</v>
       </c>
       <c r="O6" t="n">
-        <v>3.647985655272353</v>
+        <v>3.64156387306628</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1915332570841</v>
+        <v>329.2007419960299</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25135,28 +25227,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2080400574374809</v>
+        <v>0.2068495830153247</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1179350543183094</v>
+        <v>0.1176428205049618</v>
       </c>
       <c r="M7" t="n">
-        <v>3.263480687454273</v>
+        <v>3.256989862168368</v>
       </c>
       <c r="N7" t="n">
-        <v>18.42982151581995</v>
+        <v>18.36745425672842</v>
       </c>
       <c r="O7" t="n">
-        <v>4.292996798952911</v>
+        <v>4.285726806123836</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6446504477158</v>
+        <v>323.657217166656</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25213,28 +25305,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3589211812820621</v>
+        <v>0.3587365052753432</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2678721003441894</v>
+        <v>0.2694665044317677</v>
       </c>
       <c r="M8" t="n">
-        <v>3.448612830055589</v>
+        <v>3.437070072366216</v>
       </c>
       <c r="N8" t="n">
-        <v>20.04597565955448</v>
+        <v>19.96857909235156</v>
       </c>
       <c r="O8" t="n">
-        <v>4.477273239322622</v>
+        <v>4.468621609887276</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1392331376741</v>
+        <v>320.1411810162866</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25291,28 +25383,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.368371841929328</v>
+        <v>0.3669735433964644</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2154688736997383</v>
+        <v>0.2156574828693367</v>
       </c>
       <c r="M9" t="n">
-        <v>3.798922675667043</v>
+        <v>3.790967814501699</v>
       </c>
       <c r="N9" t="n">
-        <v>28.12989015892652</v>
+        <v>28.03311820719933</v>
       </c>
       <c r="O9" t="n">
-        <v>5.303761887465021</v>
+        <v>5.294631073757579</v>
       </c>
       <c r="P9" t="n">
-        <v>314.291435289916</v>
+        <v>314.3061959091012</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25350,7 +25442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51817,6 +51909,110 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-46.383226535966905,168.0094014036341</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-46.3831253606022,168.00853068006617</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-46.38304413065052,168.0077936157346</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-46.3828292082734,168.00699448356875</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-46.38250467761689,168.00622248350882</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-46.38218115217345,168.00545531190406</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-46.38188697294718,168.0046478488021</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-46.38165169591574,168.00380336462888</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-46.38323560587217,168.00940104491974</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-46.383129115388286,168.00853014421529</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-46.383045677198396,168.00779257218565</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-46.382834755323934,168.00698851197205</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-46.3825109353113,168.00621662518864</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-46.3821893702687,168.00544786029795</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-46.38189524982871,168.00464216811696</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-46.38166207777418,168.0037982899918</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J511"/>
+  <dimension ref="A1:J512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18838,6 +18838,42 @@
       <c r="J511" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="C512" t="n">
+        <v>311.31</v>
+      </c>
+      <c r="D512" t="n">
+        <v>308.02</v>
+      </c>
+      <c r="E512" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="F512" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="G512" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="H512" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="I512" t="n">
+        <v>320.82</v>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24665,6 +24701,16 @@
       </c>
       <c r="B581" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -24833,28 +24879,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07733795493044909</v>
+        <v>-0.0782541920325913</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01298361005478232</v>
+        <v>0.01334445693723496</v>
       </c>
       <c r="M2" t="n">
-        <v>4.128888161270453</v>
+        <v>4.124599875775852</v>
       </c>
       <c r="N2" t="n">
-        <v>26.02405332629732</v>
+        <v>25.98352038849761</v>
       </c>
       <c r="O2" t="n">
-        <v>5.101377591033359</v>
+        <v>5.097403298592099</v>
       </c>
       <c r="P2" t="n">
-        <v>328.70822881445</v>
+        <v>328.7179417387475</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24911,28 +24957,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2634863421944866</v>
+        <v>-0.2635139073125859</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1115573174620068</v>
+        <v>0.1120372166234218</v>
       </c>
       <c r="M3" t="n">
-        <v>4.603287709969972</v>
+        <v>4.59438155444951</v>
       </c>
       <c r="N3" t="n">
-        <v>31.64522887518218</v>
+        <v>31.58331024278774</v>
       </c>
       <c r="O3" t="n">
-        <v>5.625409218464216</v>
+        <v>5.619903045675054</v>
       </c>
       <c r="P3" t="n">
-        <v>318.5366274128198</v>
+        <v>318.5369196274711</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24989,28 +25035,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2859646913539473</v>
+        <v>-0.2860119676273507</v>
       </c>
       <c r="J4" t="n">
+        <v>511</v>
+      </c>
+      <c r="K4" t="n">
         <v>510</v>
       </c>
-      <c r="K4" t="n">
-        <v>509</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.16869095787019</v>
+        <v>0.169388716917464</v>
       </c>
       <c r="M4" t="n">
-        <v>3.901905190190914</v>
+        <v>3.89443049128786</v>
       </c>
       <c r="N4" t="n">
-        <v>22.91945801186486</v>
+        <v>22.87454531464586</v>
       </c>
       <c r="O4" t="n">
-        <v>4.787427076401777</v>
+        <v>4.782734083622658</v>
       </c>
       <c r="P4" t="n">
-        <v>315.9052904939148</v>
+        <v>315.905793967171</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -25071,28 +25117,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1084794320353449</v>
+        <v>-0.1081128902081222</v>
       </c>
       <c r="J5" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K5" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04335684068723167</v>
+        <v>0.04326330515442911</v>
       </c>
       <c r="M5" t="n">
-        <v>2.957193094328434</v>
+        <v>2.95338779369602</v>
       </c>
       <c r="N5" t="n">
-        <v>14.86099263623957</v>
+        <v>14.83357404686879</v>
       </c>
       <c r="O5" t="n">
-        <v>3.854995802363418</v>
+        <v>3.851437919383979</v>
       </c>
       <c r="P5" t="n">
-        <v>331.1748364702594</v>
+        <v>331.1709508024434</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25149,28 +25195,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06551489556220545</v>
+        <v>0.06479117652189503</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01818834146760917</v>
+        <v>0.01786823686805084</v>
       </c>
       <c r="M6" t="n">
-        <v>2.557473330383518</v>
+        <v>2.556359887786912</v>
       </c>
       <c r="N6" t="n">
-        <v>13.26098744162149</v>
+        <v>13.24152181866655</v>
       </c>
       <c r="O6" t="n">
-        <v>3.64156387306628</v>
+        <v>3.638890190520531</v>
       </c>
       <c r="P6" t="n">
-        <v>329.2007419960299</v>
+        <v>329.2084140584631</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25227,28 +25273,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2068495830153247</v>
+        <v>0.2058990848448324</v>
       </c>
       <c r="J7" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K7" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1176428205049618</v>
+        <v>0.1171043754148015</v>
       </c>
       <c r="M7" t="n">
-        <v>3.256989862168368</v>
+        <v>3.255654732770633</v>
       </c>
       <c r="N7" t="n">
-        <v>18.36745425672842</v>
+        <v>18.34269680061467</v>
       </c>
       <c r="O7" t="n">
-        <v>4.285726806123836</v>
+        <v>4.282837470721329</v>
       </c>
       <c r="P7" t="n">
-        <v>323.657217166656</v>
+        <v>323.6672932886046</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25305,28 +25351,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3587365052753432</v>
+        <v>0.3581202745221556</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K8" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2694665044317677</v>
+        <v>0.2696534679267348</v>
       </c>
       <c r="M8" t="n">
-        <v>3.437070072366216</v>
+        <v>3.433359444867423</v>
       </c>
       <c r="N8" t="n">
-        <v>19.96857909235156</v>
+        <v>19.93420366857534</v>
       </c>
       <c r="O8" t="n">
-        <v>4.468621609887276</v>
+        <v>4.464773641359137</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1411810162866</v>
+        <v>320.1477136077322</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25383,28 +25429,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3669735433964644</v>
+        <v>0.3656053164274508</v>
       </c>
       <c r="J9" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K9" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2156574828693367</v>
+        <v>0.2150365184429995</v>
       </c>
       <c r="M9" t="n">
-        <v>3.790967814501699</v>
+        <v>3.790270158877957</v>
       </c>
       <c r="N9" t="n">
-        <v>28.03311820719933</v>
+        <v>28.00143895929592</v>
       </c>
       <c r="O9" t="n">
-        <v>5.294631073757579</v>
+        <v>5.29163858925531</v>
       </c>
       <c r="P9" t="n">
-        <v>314.3061959091012</v>
+        <v>314.3207003260702</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25442,7 +25488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J511"/>
+  <dimension ref="A1:J512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52013,6 +52059,58 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-46.38321791506684,168.00940174459012</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-46.383110877855756,168.00853274691877</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-46.38302239758165,168.00780828033723</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-46.382825246094214,168.00699874899416</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-46.38250226501172,168.00622474213793</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-46.382178488901715,168.00545772677592</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-46.381880643566966,168.00465219285422</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-46.38164267561224,168.00380777373812</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
